--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,48 +772,48 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135255201</v>
+        <v>135261483</v>
       </c>
       <c r="B3" t="n">
-        <v>91937</v>
+        <v>91974</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597994</v>
+        <v>597962</v>
       </c>
       <c r="R3" t="n">
-        <v>7071669</v>
+        <v>7071674</v>
       </c>
       <c r="S3" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -840,9 +840,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -857,60 +867,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135256316</v>
+        <v>135261485</v>
       </c>
       <c r="B4" t="n">
-        <v>79373</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>598257</v>
+        <v>597961</v>
       </c>
       <c r="R4" t="n">
-        <v>7071764</v>
+        <v>7071670</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -937,9 +947,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -954,60 +974,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135256701</v>
+        <v>135277159</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598315</v>
+        <v>598084</v>
       </c>
       <c r="R5" t="n">
-        <v>7071766</v>
+        <v>7071706</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1034,9 +1054,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1051,57 +1081,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135256249</v>
+        <v>135255201</v>
       </c>
       <c r="B6" t="n">
-        <v>79130</v>
+        <v>91937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598246</v>
+        <v>597994</v>
       </c>
       <c r="R6" t="n">
-        <v>7071730</v>
+        <v>7071669</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1160,50 +1190,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135255232</v>
+        <v>135256316</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597993</v>
+        <v>598257</v>
       </c>
       <c r="R7" t="n">
-        <v>7071670</v>
+        <v>7071764</v>
       </c>
       <c r="S7" t="n">
         <v>15</v>
@@ -1262,50 +1287,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135256280</v>
+        <v>135256701</v>
       </c>
       <c r="B8" t="n">
-        <v>57972</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598255</v>
+        <v>598315</v>
       </c>
       <c r="R8" t="n">
-        <v>7071787</v>
+        <v>7071766</v>
       </c>
       <c r="S8" t="n">
         <v>15</v>
@@ -1364,53 +1384,51 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135256904</v>
+        <v>135261486</v>
       </c>
       <c r="B9" t="n">
-        <v>57975</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598036</v>
+        <v>598012</v>
       </c>
       <c r="R9" t="n">
-        <v>7071747</v>
+        <v>7071666</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1437,14 +1455,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:58</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1453,28 +1476,44 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135256186</v>
+        <v>135277153</v>
       </c>
       <c r="B10" t="n">
-        <v>99195</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1482,46 +1521,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598186</v>
+        <v>597958</v>
       </c>
       <c r="R10" t="n">
-        <v>7071740</v>
+        <v>7071702</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1548,9 +1578,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1565,15 +1605,2216 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>135277160</v>
+      </c>
+      <c r="B11" t="n">
+        <v>83358</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6440</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Vitgrynig nållav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Chaenotheca subroscida</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Eitner) Zahlbr.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>598111</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7071757</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>135256249</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79130</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>598246</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7071730</v>
+      </c>
+      <c r="S12" t="n">
+        <v>15</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>Daniel Rutschman</t>
         </is>
       </c>
-      <c r="AY10" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>135261492</v>
+      </c>
+      <c r="B13" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>597943</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7071647</v>
+      </c>
+      <c r="S13" t="n">
+        <v>3</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>135277156</v>
+      </c>
+      <c r="B14" t="n">
+        <v>80488</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>598036</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7071669</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>135261487</v>
+      </c>
+      <c r="B15" t="n">
+        <v>80492</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>6461</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Norrlandslav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Nephroma arcticum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) Torss.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>598020</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7071672</v>
+      </c>
+      <c r="S15" t="n">
+        <v>3</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Markus Borja, William Lord</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>135277157</v>
+      </c>
+      <c r="B16" t="n">
+        <v>80493</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>598034</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7071665</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>135255232</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>597993</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7071670</v>
+      </c>
+      <c r="S17" t="n">
+        <v>15</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>135256280</v>
+      </c>
+      <c r="B18" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>598255</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7071787</v>
+      </c>
+      <c r="S18" t="n">
+        <v>15</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>135261489</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>598336</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7071734</v>
+      </c>
+      <c r="S19" t="n">
+        <v>3</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>135277139</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>597949</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7071707</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135256904</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>598036</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7071747</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135261482</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597948</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7071677</v>
+      </c>
+      <c r="S22" t="n">
+        <v>3</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135261491</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>597985</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S23" t="n">
+        <v>3</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135261493</v>
+      </c>
+      <c r="B24" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597900</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7071691</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Markus Borja, William Lord, Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135256186</v>
+      </c>
+      <c r="B25" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>598186</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7071740</v>
+      </c>
+      <c r="S25" t="n">
+        <v>15</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135261481</v>
+      </c>
+      <c r="B26" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7071680</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135261488</v>
+      </c>
+      <c r="B27" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>598051</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7071709</v>
+      </c>
+      <c r="S27" t="n">
+        <v>3</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135261490</v>
+      </c>
+      <c r="B28" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597995</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7071636</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135277154</v>
+      </c>
+      <c r="B29" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7071725</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135277158</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>598024</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7071673</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY30"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1724,7 +1724,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135256249</v>
+        <v>135255152</v>
       </c>
       <c r="B12" t="n">
         <v>79130</v>
@@ -1755,14 +1755,14 @@
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598246</v>
+        <v>597979</v>
       </c>
       <c r="R12" t="n">
-        <v>7071730</v>
+        <v>7071668</v>
       </c>
       <c r="S12" t="n">
         <v>15</v>
@@ -1821,10 +1821,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135261492</v>
+        <v>135256249</v>
       </c>
       <c r="B13" t="n">
-        <v>80488</v>
+        <v>79130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1832,40 +1832,37 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597943</v>
+        <v>598246</v>
       </c>
       <c r="R13" t="n">
-        <v>7071647</v>
+        <v>7071730</v>
       </c>
       <c r="S13" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -1892,62 +1889,36 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ13" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO13" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135277156</v>
+        <v>135261492</v>
       </c>
       <c r="B14" t="n">
         <v>80488</v>
@@ -1976,19 +1947,22 @@
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>598036</v>
+        <v>597943</v>
       </c>
       <c r="R14" t="n">
-        <v>7071669</v>
+        <v>7071647</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2017,7 +1991,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2027,7 +2001,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>19:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2036,69 +2010,82 @@
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135261487</v>
+        <v>135277156</v>
       </c>
       <c r="B15" t="n">
-        <v>80492</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6461</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598020</v>
+        <v>598036</v>
       </c>
       <c r="R15" t="n">
-        <v>7071672</v>
+        <v>7071669</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2127,7 +2114,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2137,7 +2124,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2146,29 +2133,28 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Markus Borja, William Lord</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135277157</v>
+        <v>135261487</v>
       </c>
       <c r="B16" t="n">
-        <v>80493</v>
+        <v>80492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2176,37 +2162,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598034</v>
+        <v>598020</v>
       </c>
       <c r="R16" t="n">
-        <v>7071665</v>
+        <v>7071672</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2235,7 +2224,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2245,7 +2234,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2254,28 +2243,29 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja, William Lord</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135255232</v>
+        <v>135277157</v>
       </c>
       <c r="B17" t="n">
-        <v>57972</v>
+        <v>80493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2283,42 +2273,37 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>597993</v>
+        <v>598034</v>
       </c>
       <c r="R17" t="n">
-        <v>7071670</v>
+        <v>7071665</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2345,9 +2330,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2362,19 +2357,19 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135256280</v>
+        <v>135255036</v>
       </c>
       <c r="B18" t="n">
         <v>57972</v>
@@ -2410,14 +2405,14 @@
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598255</v>
+        <v>597950</v>
       </c>
       <c r="R18" t="n">
-        <v>7071787</v>
+        <v>7071688</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2476,7 +2471,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135261489</v>
+        <v>135255232</v>
       </c>
       <c r="B19" t="n">
         <v>57972</v>
@@ -2505,27 +2500,24 @@
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>598336</v>
+        <v>597993</v>
       </c>
       <c r="R19" t="n">
-        <v>7071734</v>
+        <v>7071670</v>
       </c>
       <c r="S19" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2552,19 +2544,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>18:40</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2579,19 +2561,19 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135277139</v>
+        <v>135256280</v>
       </c>
       <c r="B20" t="n">
         <v>57972</v>
@@ -2627,17 +2609,17 @@
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>597949</v>
+        <v>598255</v>
       </c>
       <c r="R20" t="n">
-        <v>7071707</v>
+        <v>7071787</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2664,19 +2646,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>17:43</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2691,39 +2663,39 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135256904</v>
+        <v>135261489</v>
       </c>
       <c r="B21" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2732,24 +2704,27 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>598036</v>
+        <v>598336</v>
       </c>
       <c r="R21" t="n">
-        <v>7071747</v>
+        <v>7071734</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2776,14 +2751,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:40</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2798,39 +2778,39 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135261482</v>
+        <v>135277139</v>
       </c>
       <c r="B22" t="n">
-        <v>57975</v>
+        <v>57972</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -2839,27 +2819,24 @@
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>597948</v>
+        <v>597949</v>
       </c>
       <c r="R22" t="n">
-        <v>7071677</v>
+        <v>7071707</v>
       </c>
       <c r="S22" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2888,7 +2865,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:49</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2898,12 +2875,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2918,19 +2890,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Markus Borja, Elin Pöllänen</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135261491</v>
+        <v>135256904</v>
       </c>
       <c r="B23" t="n">
         <v>57975</v>
@@ -2959,27 +2931,24 @@
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>färska spår</t>
         </is>
       </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>597985</v>
+        <v>598036</v>
       </c>
       <c r="R23" t="n">
-        <v>7071632</v>
+        <v>7071747</v>
       </c>
       <c r="S23" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3006,24 +2975,14 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
       <c r="AC23" t="inlineStr">
         <is>
-          <t>Färska ringhack på tall</t>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3038,22 +2997,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135261493</v>
+        <v>135261482</v>
       </c>
       <c r="B24" t="n">
-        <v>58136</v>
+        <v>57975</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3061,50 +3020,42 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>597900</v>
+        <v>597948</v>
       </c>
       <c r="R24" t="n">
-        <v>7071691</v>
+        <v>7071677</v>
       </c>
       <c r="S24" t="n">
         <v>3</v>
@@ -3136,7 +3087,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:49</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3146,7 +3097,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>19:28</t>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3166,64 +3122,63 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Markus Borja, William Lord, Elin Pöllänen</t>
+          <t>Markus Borja, Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135256186</v>
+        <v>135261491</v>
       </c>
       <c r="B25" t="n">
-        <v>99195</v>
+        <v>57975</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>598186</v>
+        <v>597985</v>
       </c>
       <c r="R25" t="n">
-        <v>7071740</v>
+        <v>7071632</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3250,9 +3205,24 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3267,57 +3237,73 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135261481</v>
+        <v>135261493</v>
       </c>
       <c r="B26" t="n">
-        <v>98060</v>
+        <v>58136</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>221945</v>
+        <v>103021</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>597961</v>
+        <v>597900</v>
       </c>
       <c r="R26" t="n">
-        <v>7071680</v>
+        <v>7071691</v>
       </c>
       <c r="S26" t="n">
         <v>3</v>
@@ -3349,7 +3335,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3359,7 +3345,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:45</t>
+          <t>19:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3379,55 +3365,64 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Markus Borja, William Lord, Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135261488</v>
+        <v>135256186</v>
       </c>
       <c r="B27" t="n">
-        <v>98060</v>
+        <v>99195</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>221945</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>598051</v>
+        <v>598186</v>
       </c>
       <c r="R27" t="n">
-        <v>7071709</v>
+        <v>7071740</v>
       </c>
       <c r="S27" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3454,19 +3449,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>18:08</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>18:08</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3481,60 +3466,57 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135261490</v>
+        <v>135261481</v>
       </c>
       <c r="B28" t="n">
-        <v>79131</v>
+        <v>98060</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>597995</v>
+        <v>597961</v>
       </c>
       <c r="R28" t="n">
-        <v>7071636</v>
+        <v>7071680</v>
       </c>
       <c r="S28" t="n">
         <v>3</v>
@@ -3566,7 +3548,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3576,7 +3558,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>19:06</t>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3585,7 +3567,6 @@
       <c r="AE28" t="b">
         <v>0</v>
       </c>
-      <c r="AF28" t="inlineStr"/>
       <c r="AG28" t="b">
         <v>0</v>
       </c>
@@ -3597,55 +3578,55 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135277154</v>
+        <v>135261488</v>
       </c>
       <c r="B29" t="n">
-        <v>79131</v>
+        <v>98060</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>228912</v>
+        <v>221945</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>597961</v>
+        <v>598051</v>
       </c>
       <c r="R29" t="n">
-        <v>7071725</v>
+        <v>7071709</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3674,7 +3655,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3684,7 +3665,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:08</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3699,22 +3680,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135277158</v>
+        <v>135261490</v>
       </c>
       <c r="B30" t="n">
-        <v>79396</v>
+        <v>79131</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3722,37 +3703,40 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>260591</v>
+        <v>228912</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>598024</v>
+        <v>597995</v>
       </c>
       <c r="R30" t="n">
-        <v>7071673</v>
+        <v>7071636</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3781,7 +3765,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3791,7 +3775,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:02</t>
+          <t>19:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3800,21 +3784,236 @@
       <c r="AE30" t="b">
         <v>0</v>
       </c>
+      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135277154</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7071725</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
           <t>Anne-Katrin Würthele</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
+      <c r="AX31" t="inlineStr">
         <is>
           <t>Anne-Katrin Würthele</t>
         </is>
       </c>
-      <c r="AY30" t="inlineStr"/>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135277158</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>598024</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7071673</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135261483</v>
+        <v>135277159</v>
       </c>
       <c r="B3" t="n">
         <v>91974</v>
@@ -803,17 +803,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597962</v>
+        <v>598084</v>
       </c>
       <c r="R3" t="n">
-        <v>7071674</v>
+        <v>7071706</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,60 +867,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135261485</v>
+        <v>135255201</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597961</v>
+        <v>597994</v>
       </c>
       <c r="R4" t="n">
-        <v>7071670</v>
+        <v>7071669</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +947,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,60 +964,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135277159</v>
+        <v>135256316</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598084</v>
+        <v>598257</v>
       </c>
       <c r="R5" t="n">
-        <v>7071706</v>
+        <v>7071764</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1044,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,57 +1061,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135255201</v>
+        <v>135256701</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597994</v>
+        <v>598315</v>
       </c>
       <c r="R6" t="n">
-        <v>7071669</v>
+        <v>7071766</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1190,7 +1170,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135256316</v>
+        <v>135277153</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1221,17 +1201,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598257</v>
+        <v>597958</v>
       </c>
       <c r="R7" t="n">
-        <v>7071764</v>
+        <v>7071702</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,9 +1238,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,60 +1265,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135256701</v>
+        <v>135277160</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>83358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598315</v>
+        <v>598111</v>
       </c>
       <c r="R8" t="n">
-        <v>7071766</v>
+        <v>7071757</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1355,9 +1345,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,63 +1372,60 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135261486</v>
+        <v>135255152</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598012</v>
+        <v>597979</v>
       </c>
       <c r="R9" t="n">
-        <v>7071666</v>
+        <v>7071668</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1455,103 +1452,77 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135277153</v>
+        <v>135256249</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597958</v>
+        <v>598246</v>
       </c>
       <c r="R10" t="n">
-        <v>7071702</v>
+        <v>7071730</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1578,19 +1549,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,22 +1566,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135277160</v>
+        <v>135277156</v>
       </c>
       <c r="B11" t="n">
-        <v>83358</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,21 +1589,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1613,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598111</v>
+        <v>598036</v>
       </c>
       <c r="R11" t="n">
-        <v>7071757</v>
+        <v>7071669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,7 +1648,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1697,7 +1658,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1724,48 +1685,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135255152</v>
+        <v>135277157</v>
       </c>
       <c r="B12" t="n">
-        <v>79130</v>
+        <v>80493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597979</v>
+        <v>598034</v>
       </c>
       <c r="R12" t="n">
-        <v>7071668</v>
+        <v>7071665</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1792,9 +1753,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,57 +1780,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135256249</v>
+        <v>135255036</v>
       </c>
       <c r="B13" t="n">
-        <v>79130</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598246</v>
+        <v>597950</v>
       </c>
       <c r="R13" t="n">
-        <v>7071730</v>
+        <v>7071688</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1918,51 +1894,53 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135261492</v>
+        <v>135255232</v>
       </c>
       <c r="B14" t="n">
-        <v>80488</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597943</v>
+        <v>597993</v>
       </c>
       <c r="R14" t="n">
-        <v>7071647</v>
+        <v>7071670</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,103 +1967,82 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135277156</v>
+        <v>135256280</v>
       </c>
       <c r="B15" t="n">
-        <v>80488</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598036</v>
+        <v>598255</v>
       </c>
       <c r="R15" t="n">
-        <v>7071669</v>
+        <v>7071787</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,19 +2069,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,22 +2086,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135261487</v>
+        <v>135277139</v>
       </c>
       <c r="B16" t="n">
-        <v>80492</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,40 +2109,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598020</v>
+        <v>597949</v>
       </c>
       <c r="R16" t="n">
-        <v>7071672</v>
+        <v>7071707</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2224,7 +2173,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2234,7 +2183,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,67 +2192,71 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, William Lord</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135277157</v>
+        <v>135256904</v>
       </c>
       <c r="B17" t="n">
-        <v>80493</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598034</v>
+        <v>598036</v>
       </c>
       <c r="R17" t="n">
-        <v>7071665</v>
+        <v>7071747</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2330,19 +2283,14 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:57</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,62 +2305,66 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135255036</v>
+        <v>135256186</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597950</v>
+        <v>598186</v>
       </c>
       <c r="R18" t="n">
-        <v>7071688</v>
+        <v>7071740</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2471,53 +2423,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135255232</v>
+        <v>135277154</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>79131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597993</v>
+        <v>597961</v>
       </c>
       <c r="R19" t="n">
-        <v>7071670</v>
+        <v>7071725</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,9 +2491,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2561,65 +2518,60 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135256280</v>
+        <v>135277158</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>79396</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>260591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598255</v>
+        <v>598024</v>
       </c>
       <c r="R20" t="n">
-        <v>7071787</v>
+        <v>7071673</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2646,9 +2598,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,1357 +2625,15 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135261489</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57972</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>598336</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7071734</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135277139</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57972</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>597949</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7071707</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>135256904</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>598036</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7071747</v>
-      </c>
-      <c r="S23" t="n">
-        <v>15</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135261482</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>597948</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7071677</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>135261491</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>597985</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7071632</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>135261493</v>
-      </c>
-      <c r="B26" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>597900</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7071691</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Markus Borja, William Lord, Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>135256186</v>
-      </c>
-      <c r="B27" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>598186</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7071740</v>
-      </c>
-      <c r="S27" t="n">
-        <v>15</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>135261481</v>
-      </c>
-      <c r="B28" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>597961</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7071680</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>135261488</v>
-      </c>
-      <c r="B29" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>598051</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7071709</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>135261490</v>
-      </c>
-      <c r="B30" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>597995</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7071636</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>135277154</v>
-      </c>
-      <c r="B31" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>597961</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7071725</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>135277158</v>
-      </c>
-      <c r="B32" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>598024</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7071673</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135277159</v>
+        <v>135261483</v>
       </c>
       <c r="B3" t="n">
         <v>91974</v>
@@ -803,17 +803,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598084</v>
+        <v>597962</v>
       </c>
       <c r="R3" t="n">
-        <v>7071706</v>
+        <v>7071674</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,7 +842,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +852,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,60 +867,60 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135255201</v>
+        <v>135261485</v>
       </c>
       <c r="B4" t="n">
-        <v>91937</v>
+        <v>91974</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597994</v>
+        <v>597961</v>
       </c>
       <c r="R4" t="n">
-        <v>7071669</v>
+        <v>7071670</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,9 +947,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -964,60 +974,60 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135256316</v>
+        <v>135277159</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>91974</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598257</v>
+        <v>598084</v>
       </c>
       <c r="R5" t="n">
-        <v>7071764</v>
+        <v>7071706</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1044,9 +1054,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1061,57 +1081,57 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135256701</v>
+        <v>135255201</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>91937</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598315</v>
+        <v>597994</v>
       </c>
       <c r="R6" t="n">
-        <v>7071766</v>
+        <v>7071669</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1170,7 +1190,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135277153</v>
+        <v>135256316</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1201,17 +1221,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597958</v>
+        <v>598257</v>
       </c>
       <c r="R7" t="n">
-        <v>7071702</v>
+        <v>7071764</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1238,19 +1258,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,60 +1275,60 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135277160</v>
+        <v>135256701</v>
       </c>
       <c r="B8" t="n">
-        <v>83358</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598111</v>
+        <v>598315</v>
       </c>
       <c r="R8" t="n">
-        <v>7071757</v>
+        <v>7071766</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1345,19 +1355,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,60 +1372,63 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135255152</v>
+        <v>135261486</v>
       </c>
       <c r="B9" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597979</v>
+        <v>598012</v>
       </c>
       <c r="R9" t="n">
-        <v>7071668</v>
+        <v>7071666</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1452,77 +1455,103 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135256249</v>
+        <v>135277153</v>
       </c>
       <c r="B10" t="n">
-        <v>79130</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598246</v>
+        <v>597958</v>
       </c>
       <c r="R10" t="n">
-        <v>7071730</v>
+        <v>7071702</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1549,9 +1578,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1566,22 +1605,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135277156</v>
+        <v>135277160</v>
       </c>
       <c r="B11" t="n">
-        <v>80488</v>
+        <v>83358</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1589,21 +1628,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1613,10 +1652,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598036</v>
+        <v>598111</v>
       </c>
       <c r="R11" t="n">
-        <v>7071669</v>
+        <v>7071757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1648,7 +1687,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1658,7 +1697,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1685,48 +1724,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135277157</v>
+        <v>135255152</v>
       </c>
       <c r="B12" t="n">
-        <v>80493</v>
+        <v>79130</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598034</v>
+        <v>597979</v>
       </c>
       <c r="R12" t="n">
-        <v>7071665</v>
+        <v>7071668</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1753,19 +1792,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1780,62 +1809,57 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135255036</v>
+        <v>135256249</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>79130</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597950</v>
+        <v>598246</v>
       </c>
       <c r="R13" t="n">
-        <v>7071688</v>
+        <v>7071730</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1894,53 +1918,51 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135255232</v>
+        <v>135261492</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>80488</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597993</v>
+        <v>597943</v>
       </c>
       <c r="R14" t="n">
-        <v>7071670</v>
+        <v>7071647</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1967,82 +1989,103 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja, William Lord, Elin Pöllänen</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135256280</v>
+        <v>135277156</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>80488</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598255</v>
+        <v>598036</v>
       </c>
       <c r="R15" t="n">
-        <v>7071787</v>
+        <v>7071669</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2069,9 +2112,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2086,22 +2139,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135277139</v>
+        <v>135261487</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>80492</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2109,42 +2162,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597949</v>
+        <v>598020</v>
       </c>
       <c r="R16" t="n">
-        <v>7071707</v>
+        <v>7071672</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2173,7 +2224,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2183,7 +2234,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2192,71 +2243,67 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja, William Lord</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135256904</v>
+        <v>135277157</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>80493</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598036</v>
+        <v>598034</v>
       </c>
       <c r="R17" t="n">
-        <v>7071747</v>
+        <v>7071665</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2283,14 +2330,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2305,66 +2357,62 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135256186</v>
+        <v>135255036</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>57972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598186</v>
+        <v>597950</v>
       </c>
       <c r="R18" t="n">
-        <v>7071740</v>
+        <v>7071688</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2423,48 +2471,53 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135277154</v>
+        <v>135255232</v>
       </c>
       <c r="B19" t="n">
-        <v>79131</v>
+        <v>57972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597961</v>
+        <v>597993</v>
       </c>
       <c r="R19" t="n">
-        <v>7071725</v>
+        <v>7071670</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2491,19 +2544,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2518,60 +2561,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135277158</v>
+        <v>135256280</v>
       </c>
       <c r="B20" t="n">
-        <v>79396</v>
+        <v>57972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>260591</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598024</v>
+        <v>598255</v>
       </c>
       <c r="R20" t="n">
-        <v>7071673</v>
+        <v>7071787</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2598,19 +2646,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2625,15 +2663,1357 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135261489</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>598336</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7071734</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135277139</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57972</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597949</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7071707</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
           <t>Anne-Katrin Würthele</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
+      <c r="AX22" t="inlineStr">
         <is>
           <t>Anne-Katrin Würthele</t>
         </is>
       </c>
-      <c r="AY20" t="inlineStr"/>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135256904</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>598036</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7071747</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135261482</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597948</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7071677</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135261491</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57975</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>597985</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135261493</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58136</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597900</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7071691</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Markus Borja, William Lord, Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135256186</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99195</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>598186</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7071740</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135261481</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7071680</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135261488</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98060</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>598051</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7071709</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135261490</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597995</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7071636</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135277154</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79131</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7071725</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135277158</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79396</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>598024</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7071673</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -2037,7 +2037,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja, William Lord, Elin Pöllänen</t>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>

--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,10 +774,15 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255191</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135261483</v>
+        <v>135277159</v>
       </c>
       <c r="B3" t="n">
         <v>91974</v>
@@ -803,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597962</v>
+        <v>598084</v>
       </c>
       <c r="R3" t="n">
-        <v>7071674</v>
+        <v>7071706</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -842,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -852,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -867,60 +877,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277159</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135261485</v>
+        <v>135255201</v>
       </c>
       <c r="B4" t="n">
-        <v>91974</v>
+        <v>91937</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597961</v>
+        <v>597994</v>
       </c>
       <c r="R4" t="n">
-        <v>7071670</v>
+        <v>7071669</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -947,19 +962,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -974,60 +979,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255201</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135277159</v>
+        <v>135256316</v>
       </c>
       <c r="B5" t="n">
-        <v>91974</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598084</v>
+        <v>598257</v>
       </c>
       <c r="R5" t="n">
-        <v>7071706</v>
+        <v>7071764</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1054,19 +1064,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,57 +1081,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256316</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135255201</v>
+        <v>135256701</v>
       </c>
       <c r="B6" t="n">
-        <v>91937</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597994</v>
+        <v>598315</v>
       </c>
       <c r="R6" t="n">
-        <v>7071669</v>
+        <v>7071766</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1187,10 +1192,15 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256701</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135256316</v>
+        <v>135277153</v>
       </c>
       <c r="B7" t="n">
         <v>79373</v>
@@ -1221,17 +1231,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598257</v>
+        <v>597958</v>
       </c>
       <c r="R7" t="n">
-        <v>7071764</v>
+        <v>7071702</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1258,9 +1268,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1275,60 +1295,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277153</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135256701</v>
+        <v>135277160</v>
       </c>
       <c r="B8" t="n">
-        <v>79373</v>
+        <v>83358</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598315</v>
+        <v>598111</v>
       </c>
       <c r="R8" t="n">
-        <v>7071766</v>
+        <v>7071757</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1355,9 +1380,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1372,63 +1407,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277160</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135261486</v>
+        <v>135255152</v>
       </c>
       <c r="B9" t="n">
-        <v>79373</v>
+        <v>79130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598012</v>
+        <v>597979</v>
       </c>
       <c r="R9" t="n">
-        <v>7071666</v>
+        <v>7071668</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1455,103 +1492,82 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255152</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135277153</v>
+        <v>135256249</v>
       </c>
       <c r="B10" t="n">
-        <v>79373</v>
+        <v>79130</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597958</v>
+        <v>598246</v>
       </c>
       <c r="R10" t="n">
-        <v>7071702</v>
+        <v>7071730</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1578,19 +1594,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1605,22 +1611,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256249</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135277160</v>
+        <v>135277156</v>
       </c>
       <c r="B11" t="n">
-        <v>83358</v>
+        <v>80488</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1628,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1652,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598111</v>
+        <v>598036</v>
       </c>
       <c r="R11" t="n">
-        <v>7071757</v>
+        <v>7071669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1687,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1697,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1721,51 +1732,56 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277156</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135255152</v>
+        <v>135277157</v>
       </c>
       <c r="B12" t="n">
-        <v>79130</v>
+        <v>80493</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597979</v>
+        <v>598034</v>
       </c>
       <c r="R12" t="n">
-        <v>7071668</v>
+        <v>7071665</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1792,9 +1808,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1809,57 +1835,67 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277157</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135256249</v>
+        <v>135255036</v>
       </c>
       <c r="B13" t="n">
-        <v>79130</v>
+        <v>57972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598246</v>
+        <v>597950</v>
       </c>
       <c r="R13" t="n">
-        <v>7071730</v>
+        <v>7071688</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1915,54 +1951,61 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255036</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135261492</v>
+        <v>135255232</v>
       </c>
       <c r="B14" t="n">
-        <v>80488</v>
+        <v>57972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597943</v>
+        <v>597993</v>
       </c>
       <c r="R14" t="n">
-        <v>7071647</v>
+        <v>7071670</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -1989,103 +2032,87 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135255232</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135277156</v>
+        <v>135256280</v>
       </c>
       <c r="B15" t="n">
-        <v>80488</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598036</v>
+        <v>598255</v>
       </c>
       <c r="R15" t="n">
-        <v>7071669</v>
+        <v>7071787</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2112,19 +2139,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2139,22 +2156,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256280</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135261487</v>
+        <v>135277139</v>
       </c>
       <c r="B16" t="n">
-        <v>80492</v>
+        <v>57972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2162,40 +2184,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598020</v>
+        <v>597949</v>
       </c>
       <c r="R16" t="n">
-        <v>7071672</v>
+        <v>7071707</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2224,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2234,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2243,67 +2267,76 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, William Lord</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277139</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135277157</v>
+        <v>135256904</v>
       </c>
       <c r="B17" t="n">
-        <v>80493</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598034</v>
+        <v>598036</v>
       </c>
       <c r="R17" t="n">
-        <v>7071665</v>
+        <v>7071747</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2330,19 +2363,14 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:57</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2357,62 +2385,71 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256904</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135255036</v>
+        <v>135256186</v>
       </c>
       <c r="B18" t="n">
-        <v>57972</v>
+        <v>99195</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597950</v>
+        <v>598186</v>
       </c>
       <c r="R18" t="n">
-        <v>7071688</v>
+        <v>7071740</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2468,56 +2505,56 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256186</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135255232</v>
+        <v>135277154</v>
       </c>
       <c r="B19" t="n">
-        <v>57972</v>
+        <v>79131</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597993</v>
+        <v>597961</v>
       </c>
       <c r="R19" t="n">
-        <v>7071670</v>
+        <v>7071725</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2544,9 +2581,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2561,65 +2608,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277154</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135256280</v>
+        <v>135277158</v>
       </c>
       <c r="B20" t="n">
-        <v>57972</v>
+        <v>79396</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>260591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598255</v>
+        <v>598024</v>
       </c>
       <c r="R20" t="n">
-        <v>7071787</v>
+        <v>7071673</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2646,9 +2693,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2663,1359 +2720,43 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135261489</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57972</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>598336</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7071734</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135277139</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57972</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>597949</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7071707</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>135256904</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>598036</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7071747</v>
-      </c>
-      <c r="S23" t="n">
-        <v>15</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135261482</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>597948</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7071677</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>135261491</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57975</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>597985</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7071632</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>135261493</v>
-      </c>
-      <c r="B26" t="n">
-        <v>58136</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>597900</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7071691</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Markus Borja, William Lord, Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>135256186</v>
-      </c>
-      <c r="B27" t="n">
-        <v>99195</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>598186</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7071740</v>
-      </c>
-      <c r="S27" t="n">
-        <v>15</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>135261481</v>
-      </c>
-      <c r="B28" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>597961</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7071680</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>135261488</v>
-      </c>
-      <c r="B29" t="n">
-        <v>98060</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>598051</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7071709</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>135261490</v>
-      </c>
-      <c r="B30" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>597995</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7071636</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>135277154</v>
-      </c>
-      <c r="B31" t="n">
-        <v>79131</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>597961</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7071725</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>135277158</v>
-      </c>
-      <c r="B32" t="n">
-        <v>79396</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>598024</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7071673</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277158</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135255191</v>
       </c>
       <c r="B2" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135277159</v>
+        <v>135261483</v>
       </c>
       <c r="B3" t="n">
-        <v>91974</v>
+        <v>92016</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598084</v>
+        <v>597962</v>
       </c>
       <c r="R3" t="n">
-        <v>7071706</v>
+        <v>7071674</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,65 +877,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277159</t>
+          <t>https://artportalen.se/Sighting/135261483</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135255201</v>
+        <v>135261485</v>
       </c>
       <c r="B4" t="n">
-        <v>91937</v>
+        <v>92016</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597994</v>
+        <v>597961</v>
       </c>
       <c r="R4" t="n">
-        <v>7071669</v>
+        <v>7071670</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,9 +962,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,65 +989,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255201</t>
+          <t>https://artportalen.se/Sighting/135261485</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135256316</v>
+        <v>135277159</v>
       </c>
       <c r="B5" t="n">
-        <v>79373</v>
+        <v>92016</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598257</v>
+        <v>598084</v>
       </c>
       <c r="R5" t="n">
-        <v>7071764</v>
+        <v>7071706</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,9 +1074,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,62 +1101,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256316</t>
+          <t>https://artportalen.se/Sighting/135277159</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135256701</v>
+        <v>135255201</v>
       </c>
       <c r="B6" t="n">
-        <v>79373</v>
+        <v>91979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598315</v>
+        <v>597994</v>
       </c>
       <c r="R6" t="n">
-        <v>7071766</v>
+        <v>7071669</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,16 +1214,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256701</t>
+          <t>https://artportalen.se/Sighting/135255201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135277153</v>
+        <v>135256316</v>
       </c>
       <c r="B7" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1231,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597958</v>
+        <v>598257</v>
       </c>
       <c r="R7" t="n">
-        <v>7071702</v>
+        <v>7071764</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,19 +1288,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,65 +1305,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277153</t>
+          <t>https://artportalen.se/Sighting/135256316</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135277160</v>
+        <v>135256701</v>
       </c>
       <c r="B8" t="n">
-        <v>83358</v>
+        <v>79411</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598111</v>
+        <v>598315</v>
       </c>
       <c r="R8" t="n">
-        <v>7071757</v>
+        <v>7071766</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,19 +1390,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,65 +1407,68 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277160</t>
+          <t>https://artportalen.se/Sighting/135256701</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135255152</v>
+        <v>135261486</v>
       </c>
       <c r="B9" t="n">
-        <v>79130</v>
+        <v>79411</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597979</v>
+        <v>598012</v>
       </c>
       <c r="R9" t="n">
-        <v>7071668</v>
+        <v>7071666</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1492,82 +1495,108 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255152</t>
+          <t>https://artportalen.se/Sighting/135261486</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135256249</v>
+        <v>135277153</v>
       </c>
       <c r="B10" t="n">
-        <v>79130</v>
+        <v>79411</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598246</v>
+        <v>597958</v>
       </c>
       <c r="R10" t="n">
-        <v>7071730</v>
+        <v>7071702</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1594,9 +1623,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,27 +1650,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256249</t>
+          <t>https://artportalen.se/Sighting/135277153</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135277156</v>
+        <v>135277160</v>
       </c>
       <c r="B11" t="n">
-        <v>80488</v>
+        <v>83398</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1678,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598036</v>
+        <v>598111</v>
       </c>
       <c r="R11" t="n">
-        <v>7071669</v>
+        <v>7071757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,54 +1773,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277156</t>
+          <t>https://artportalen.se/Sighting/135277160</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135277157</v>
+        <v>135255152</v>
       </c>
       <c r="B12" t="n">
-        <v>80493</v>
+        <v>79168</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598034</v>
+        <v>597979</v>
       </c>
       <c r="R12" t="n">
-        <v>7071665</v>
+        <v>7071668</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1808,19 +1847,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,67 +1864,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277157</t>
+          <t>https://artportalen.se/Sighting/135255152</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135255036</v>
+        <v>135256249</v>
       </c>
       <c r="B13" t="n">
-        <v>57972</v>
+        <v>79168</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597950</v>
+        <v>598246</v>
       </c>
       <c r="R13" t="n">
-        <v>7071688</v>
+        <v>7071730</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1953,59 +1977,57 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255036</t>
+          <t>https://artportalen.se/Sighting/135256249</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135255232</v>
+        <v>135261492</v>
       </c>
       <c r="B14" t="n">
-        <v>57972</v>
+        <v>80526</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597993</v>
+        <v>597943</v>
       </c>
       <c r="R14" t="n">
-        <v>7071670</v>
+        <v>7071647</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2032,87 +2054,108 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255232</t>
+          <t>https://artportalen.se/Sighting/135261492</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135256280</v>
+        <v>135277156</v>
       </c>
       <c r="B15" t="n">
-        <v>57972</v>
+        <v>80526</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598255</v>
+        <v>598036</v>
       </c>
       <c r="R15" t="n">
-        <v>7071787</v>
+        <v>7071669</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,9 +2182,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,27 +2209,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256280</t>
+          <t>https://artportalen.se/Sighting/135277156</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135277139</v>
+        <v>135261487</v>
       </c>
       <c r="B16" t="n">
-        <v>57972</v>
+        <v>80530</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,42 +2237,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597949</v>
+        <v>598020</v>
       </c>
       <c r="R16" t="n">
-        <v>7071707</v>
+        <v>7071672</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2299,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2309,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2267,76 +2318,72 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja, William Lord</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277139</t>
+          <t>https://artportalen.se/Sighting/135261487</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135256904</v>
+        <v>135277157</v>
       </c>
       <c r="B17" t="n">
-        <v>57975</v>
+        <v>80531</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598036</v>
+        <v>598034</v>
       </c>
       <c r="R17" t="n">
-        <v>7071747</v>
+        <v>7071665</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2363,14 +2410,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,71 +2437,67 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256904</t>
+          <t>https://artportalen.se/Sighting/135277157</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135256186</v>
+        <v>135255036</v>
       </c>
       <c r="B18" t="n">
-        <v>99195</v>
+        <v>57977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598186</v>
+        <v>597950</v>
       </c>
       <c r="R18" t="n">
-        <v>7071740</v>
+        <v>7071688</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2507,54 +2555,59 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256186</t>
+          <t>https://artportalen.se/Sighting/135255036</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135277154</v>
+        <v>135255232</v>
       </c>
       <c r="B19" t="n">
-        <v>79131</v>
+        <v>57977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597961</v>
+        <v>597993</v>
       </c>
       <c r="R19" t="n">
-        <v>7071725</v>
+        <v>7071670</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2581,19 +2634,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,65 +2651,70 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277154</t>
+          <t>https://artportalen.se/Sighting/135255232</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135277158</v>
+        <v>135256280</v>
       </c>
       <c r="B20" t="n">
-        <v>79396</v>
+        <v>57977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>260591</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598024</v>
+        <v>598255</v>
       </c>
       <c r="R20" t="n">
-        <v>7071673</v>
+        <v>7071787</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2693,19 +2741,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,16 +2758,1418 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256280</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135261489</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>598336</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7071734</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261489</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135277139</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597949</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7071707</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277139</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135256904</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>598036</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7071747</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256904</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135261482</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597948</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7071677</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261482</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135261491</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>597985</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261491</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135261493</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597900</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7071691</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Markus Borja, William Lord, Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261493</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135256186</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99242</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>598186</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7071740</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256186</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135261481</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98104</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7071680</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261481</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135261488</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98104</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>598051</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7071709</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261488</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135261490</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597995</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7071636</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261490</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135277154</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79169</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7071725</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277154</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135277158</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79434</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>598024</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7071673</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135277158</t>
         </is>
@@ -2756,6 +4196,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135255191</v>
       </c>
       <c r="B2" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>135261483</v>
       </c>
       <c r="B3" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -897,7 +897,7 @@
         <v>135261485</v>
       </c>
       <c r="B4" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1009,7 +1009,7 @@
         <v>135277159</v>
       </c>
       <c r="B5" t="n">
-        <v>92016</v>
+        <v>92043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1121,7 +1121,7 @@
         <v>135255201</v>
       </c>
       <c r="B6" t="n">
-        <v>91979</v>
+        <v>92006</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1223,7 +1223,7 @@
         <v>135256316</v>
       </c>
       <c r="B7" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1325,7 +1325,7 @@
         <v>135256701</v>
       </c>
       <c r="B8" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1427,7 +1427,7 @@
         <v>135261486</v>
       </c>
       <c r="B9" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1558,7 +1558,7 @@
         <v>135277153</v>
       </c>
       <c r="B10" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1670,7 +1670,7 @@
         <v>135277160</v>
       </c>
       <c r="B11" t="n">
-        <v>83398</v>
+        <v>83425</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1782,7 +1782,7 @@
         <v>135255152</v>
       </c>
       <c r="B12" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1884,7 +1884,7 @@
         <v>135256249</v>
       </c>
       <c r="B13" t="n">
-        <v>79168</v>
+        <v>79195</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>135261492</v>
       </c>
       <c r="B14" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2117,7 +2117,7 @@
         <v>135277156</v>
       </c>
       <c r="B15" t="n">
-        <v>80526</v>
+        <v>80553</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2229,7 +2229,7 @@
         <v>135261487</v>
       </c>
       <c r="B16" t="n">
-        <v>80530</v>
+        <v>80557</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2345,7 +2345,7 @@
         <v>135277157</v>
       </c>
       <c r="B17" t="n">
-        <v>80531</v>
+        <v>80558</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -3505,7 +3505,7 @@
         <v>135256186</v>
       </c>
       <c r="B27" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3616,7 +3616,7 @@
         <v>135261481</v>
       </c>
       <c r="B28" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>135261488</v>
       </c>
       <c r="B29" t="n">
-        <v>98104</v>
+        <v>98131</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3840,7 +3840,7 @@
         <v>135261490</v>
       </c>
       <c r="B30" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3956,7 +3956,7 @@
         <v>135277154</v>
       </c>
       <c r="B31" t="n">
-        <v>79169</v>
+        <v>79196</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4068,7 +4068,7 @@
         <v>135277158</v>
       </c>
       <c r="B32" t="n">
-        <v>79434</v>
+        <v>79461</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ32"/>
+  <dimension ref="A1:AZ20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -683,7 +683,7 @@
         <v>135255191</v>
       </c>
       <c r="B2" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -782,10 +782,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135261483</v>
+        <v>135277159</v>
       </c>
       <c r="B3" t="n">
-        <v>92048</v>
+        <v>92050</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>597962</v>
+        <v>598084</v>
       </c>
       <c r="R3" t="n">
-        <v>7071674</v>
+        <v>7071706</v>
       </c>
       <c r="S3" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>17:54</t>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,65 +877,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261483</t>
+          <t>https://artportalen.se/Sighting/135277159</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135261485</v>
+        <v>135255201</v>
       </c>
       <c r="B4" t="n">
-        <v>92048</v>
+        <v>92013</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597961</v>
+        <v>597994</v>
       </c>
       <c r="R4" t="n">
-        <v>7071670</v>
+        <v>7071669</v>
       </c>
       <c r="S4" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,19 +962,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>17:54</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -989,65 +979,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261485</t>
+          <t>https://artportalen.se/Sighting/135255201</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135277159</v>
+        <v>135256316</v>
       </c>
       <c r="B5" t="n">
-        <v>92048</v>
+        <v>79441</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598084</v>
+        <v>598257</v>
       </c>
       <c r="R5" t="n">
-        <v>7071706</v>
+        <v>7071764</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1074,19 +1064,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>18:10</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1101,62 +1081,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277159</t>
+          <t>https://artportalen.se/Sighting/135256316</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135255201</v>
+        <v>135256701</v>
       </c>
       <c r="B6" t="n">
-        <v>92011</v>
+        <v>79441</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>597994</v>
+        <v>598315</v>
       </c>
       <c r="R6" t="n">
-        <v>7071669</v>
+        <v>7071766</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1214,13 +1194,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255201</t>
+          <t>https://artportalen.se/Sighting/135256701</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135256316</v>
+        <v>135277153</v>
       </c>
       <c r="B7" t="n">
         <v>79441</v>
@@ -1251,17 +1231,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>598257</v>
+        <v>597958</v>
       </c>
       <c r="R7" t="n">
-        <v>7071764</v>
+        <v>7071702</v>
       </c>
       <c r="S7" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,9 +1268,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1305,65 +1295,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256316</t>
+          <t>https://artportalen.se/Sighting/135277153</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135256701</v>
+        <v>135277160</v>
       </c>
       <c r="B8" t="n">
-        <v>79441</v>
+        <v>83428</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6440</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598315</v>
+        <v>598111</v>
       </c>
       <c r="R8" t="n">
-        <v>7071766</v>
+        <v>7071757</v>
       </c>
       <c r="S8" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1390,9 +1380,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>18:25</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,68 +1407,65 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256701</t>
+          <t>https://artportalen.se/Sighting/135277160</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135261486</v>
+        <v>135255152</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>79198</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>598012</v>
+        <v>597979</v>
       </c>
       <c r="R9" t="n">
-        <v>7071666</v>
+        <v>7071668</v>
       </c>
       <c r="S9" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1495,108 +1492,82 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>17:58</t>
-        </is>
-      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261486</t>
+          <t>https://artportalen.se/Sighting/135255152</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135277153</v>
+        <v>135256249</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>79198</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>597958</v>
+        <v>598246</v>
       </c>
       <c r="R10" t="n">
-        <v>7071702</v>
+        <v>7071730</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1623,19 +1594,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1650,27 +1611,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277153</t>
+          <t>https://artportalen.se/Sighting/135256249</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135277160</v>
+        <v>135277156</v>
       </c>
       <c r="B11" t="n">
-        <v>83428</v>
+        <v>80556</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1678,21 +1639,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6440</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1702,10 +1663,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598111</v>
+        <v>598036</v>
       </c>
       <c r="R11" t="n">
-        <v>7071757</v>
+        <v>7071669</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1737,7 +1698,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1747,7 +1708,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>18:25</t>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1773,54 +1734,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277160</t>
+          <t>https://artportalen.se/Sighting/135277156</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135255152</v>
+        <v>135277157</v>
       </c>
       <c r="B12" t="n">
-        <v>79198</v>
+        <v>80561</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6446</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>597979</v>
+        <v>598034</v>
       </c>
       <c r="R12" t="n">
-        <v>7071668</v>
+        <v>7071665</v>
       </c>
       <c r="S12" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1847,9 +1808,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1864,62 +1835,67 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255152</t>
+          <t>https://artportalen.se/Sighting/135277157</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135256249</v>
+        <v>135255036</v>
       </c>
       <c r="B13" t="n">
-        <v>79198</v>
+        <v>57977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>598246</v>
+        <v>597950</v>
       </c>
       <c r="R13" t="n">
-        <v>7071730</v>
+        <v>7071688</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1977,57 +1953,59 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256249</t>
+          <t>https://artportalen.se/Sighting/135255036</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135261492</v>
+        <v>135255232</v>
       </c>
       <c r="B14" t="n">
-        <v>80556</v>
+        <v>57977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597943</v>
+        <v>597993</v>
       </c>
       <c r="R14" t="n">
-        <v>7071647</v>
+        <v>7071670</v>
       </c>
       <c r="S14" t="n">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2054,108 +2032,87 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>19:20</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
-      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261492</t>
+          <t>https://artportalen.se/Sighting/135255232</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135277156</v>
+        <v>135256280</v>
       </c>
       <c r="B15" t="n">
-        <v>80556</v>
+        <v>57977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598036</v>
+        <v>598255</v>
       </c>
       <c r="R15" t="n">
-        <v>7071669</v>
+        <v>7071787</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2182,19 +2139,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>17:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,27 +2156,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277156</t>
+          <t>https://artportalen.se/Sighting/135256280</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135261487</v>
+        <v>135277139</v>
       </c>
       <c r="B16" t="n">
-        <v>80560</v>
+        <v>57977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2237,40 +2184,42 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6461</v>
+        <v>100049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Norrlandslav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma arcticum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Torss.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Lill-kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>598020</v>
+        <v>597949</v>
       </c>
       <c r="R16" t="n">
-        <v>7071672</v>
+        <v>7071707</v>
       </c>
       <c r="S16" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2299,7 +2248,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2309,7 +2258,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:43</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2318,72 +2267,76 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Markus Borja</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Markus Borja, William Lord</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135261487</t>
+          <t>https://artportalen.se/Sighting/135277139</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135277157</v>
+        <v>135256904</v>
       </c>
       <c r="B17" t="n">
-        <v>80561</v>
+        <v>57980</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598034</v>
+        <v>598036</v>
       </c>
       <c r="R17" t="n">
-        <v>7071665</v>
+        <v>7071747</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2410,19 +2363,14 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>17:57</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2437,67 +2385,71 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277157</t>
+          <t>https://artportalen.se/Sighting/135256904</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135255036</v>
+        <v>135256186</v>
       </c>
       <c r="B18" t="n">
-        <v>57977</v>
+        <v>99276</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>blomning</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>597950</v>
+        <v>598186</v>
       </c>
       <c r="R18" t="n">
-        <v>7071688</v>
+        <v>7071740</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2555,59 +2507,54 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255036</t>
+          <t>https://artportalen.se/Sighting/135256186</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135255232</v>
+        <v>135277154</v>
       </c>
       <c r="B19" t="n">
-        <v>57977</v>
+        <v>79199</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100049</v>
+        <v>228912</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597993</v>
+        <v>597961</v>
       </c>
       <c r="R19" t="n">
-        <v>7071670</v>
+        <v>7071725</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2634,9 +2581,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2651,70 +2608,65 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255232</t>
+          <t>https://artportalen.se/Sighting/135277154</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135256280</v>
+        <v>135277158</v>
       </c>
       <c r="B20" t="n">
-        <v>57977</v>
+        <v>79464</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>260591</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Talltagel</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria fremontii</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598255</v>
+        <v>598024</v>
       </c>
       <c r="R20" t="n">
-        <v>7071787</v>
+        <v>7071673</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2741,9 +2693,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2758,1418 +2720,16 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135256280</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>135261489</v>
-      </c>
-      <c r="B21" t="n">
-        <v>57977</v>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E21" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q21" t="n">
-        <v>598336</v>
-      </c>
-      <c r="R21" t="n">
-        <v>7071734</v>
-      </c>
-      <c r="S21" t="n">
-        <v>3</v>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>18:40</t>
-        </is>
-      </c>
-      <c r="AD21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG21" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT21" t="inlineStr"/>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY21" t="inlineStr"/>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135261489</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>135277139</v>
-      </c>
-      <c r="B22" t="n">
-        <v>57977</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E22" t="n">
-        <v>100049</v>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Spillkråka</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q22" t="n">
-        <v>597949</v>
-      </c>
-      <c r="R22" t="n">
-        <v>7071707</v>
-      </c>
-      <c r="S22" t="n">
-        <v>10</v>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:43</t>
-        </is>
-      </c>
-      <c r="AD22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT22" t="inlineStr"/>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr"/>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135277139</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>135256904</v>
-      </c>
-      <c r="B23" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q23" t="n">
-        <v>598036</v>
-      </c>
-      <c r="R23" t="n">
-        <v>7071747</v>
-      </c>
-      <c r="S23" t="n">
-        <v>15</v>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
-        </is>
-      </c>
-      <c r="AD23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT23" t="inlineStr"/>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY23" t="inlineStr"/>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135256904</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>135261482</v>
-      </c>
-      <c r="B24" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E24" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="P24" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q24" t="n">
-        <v>597948</v>
-      </c>
-      <c r="R24" t="n">
-        <v>7071677</v>
-      </c>
-      <c r="S24" t="n">
-        <v>3</v>
-      </c>
-      <c r="T24" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V24" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W24" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y24" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AA24" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>17:49</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Äldre ringhack på gran</t>
-        </is>
-      </c>
-      <c r="AD24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT24" t="inlineStr"/>
-      <c r="AW24" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY24" t="inlineStr"/>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135261482</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>135261491</v>
-      </c>
-      <c r="B25" t="n">
-        <v>57980</v>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E25" t="n">
-        <v>100109</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Tretåig hackspett</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Picoides tridactylus</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="P25" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q25" t="n">
-        <v>597985</v>
-      </c>
-      <c r="R25" t="n">
-        <v>7071632</v>
-      </c>
-      <c r="S25" t="n">
-        <v>3</v>
-      </c>
-      <c r="T25" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V25" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W25" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y25" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AA25" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>19:11</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Färska ringhack på tall</t>
-        </is>
-      </c>
-      <c r="AD25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT25" t="inlineStr"/>
-      <c r="AW25" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
-        </is>
-      </c>
-      <c r="AY25" t="inlineStr"/>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135261491</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>135261493</v>
-      </c>
-      <c r="B26" t="n">
-        <v>58141</v>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E26" t="n">
-        <v>103021</v>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Talltita</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Poecile montanus</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
-      <c r="P26" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q26" t="n">
-        <v>597900</v>
-      </c>
-      <c r="R26" t="n">
-        <v>7071691</v>
-      </c>
-      <c r="S26" t="n">
-        <v>3</v>
-      </c>
-      <c r="T26" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U26" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V26" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W26" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y26" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>19:28</t>
-        </is>
-      </c>
-      <c r="AD26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT26" t="inlineStr"/>
-      <c r="AW26" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>Markus Borja, William Lord, Elin Pöllänen</t>
-        </is>
-      </c>
-      <c r="AY26" t="inlineStr"/>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135261493</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>135256186</v>
-      </c>
-      <c r="B27" t="n">
-        <v>99274</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E27" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
-      <c r="P27" t="inlineStr">
-        <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q27" t="n">
-        <v>598186</v>
-      </c>
-      <c r="R27" t="n">
-        <v>7071740</v>
-      </c>
-      <c r="S27" t="n">
-        <v>15</v>
-      </c>
-      <c r="T27" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U27" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W27" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y27" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AA27" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AD27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT27" t="inlineStr"/>
-      <c r="AW27" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>Daniel Rutschman</t>
-        </is>
-      </c>
-      <c r="AY27" t="inlineStr"/>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135256186</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>135261481</v>
-      </c>
-      <c r="B28" t="n">
-        <v>98136</v>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E28" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
-      <c r="P28" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q28" t="n">
-        <v>597961</v>
-      </c>
-      <c r="R28" t="n">
-        <v>7071680</v>
-      </c>
-      <c r="S28" t="n">
-        <v>3</v>
-      </c>
-      <c r="T28" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U28" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V28" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W28" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y28" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AA28" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
-      <c r="AD28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT28" t="inlineStr"/>
-      <c r="AW28" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY28" t="inlineStr"/>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135261481</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>135261488</v>
-      </c>
-      <c r="B29" t="n">
-        <v>98136</v>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>LC</t>
-        </is>
-      </c>
-      <c r="E29" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>Lycopodium annotinum</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
-      <c r="P29" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q29" t="n">
-        <v>598051</v>
-      </c>
-      <c r="R29" t="n">
-        <v>7071709</v>
-      </c>
-      <c r="S29" t="n">
-        <v>3</v>
-      </c>
-      <c r="T29" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U29" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V29" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W29" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y29" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AA29" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:08</t>
-        </is>
-      </c>
-      <c r="AD29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG29" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT29" t="inlineStr"/>
-      <c r="AW29" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135261488</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>135261490</v>
-      </c>
-      <c r="B30" t="n">
-        <v>79199</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E30" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="N30" t="inlineStr"/>
-      <c r="P30" t="inlineStr">
-        <is>
-          <t>Lill-kullberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q30" t="n">
-        <v>597995</v>
-      </c>
-      <c r="R30" t="n">
-        <v>7071636</v>
-      </c>
-      <c r="S30" t="n">
-        <v>3</v>
-      </c>
-      <c r="T30" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U30" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V30" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W30" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y30" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AA30" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>19:06</t>
-        </is>
-      </c>
-      <c r="AD30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF30" t="inlineStr"/>
-      <c r="AG30" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT30" t="inlineStr"/>
-      <c r="AW30" t="inlineStr">
-        <is>
-          <t>Markus Borja</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>Markus Borja, Elin Pöllänen, William Lord</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135261490</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>135277154</v>
-      </c>
-      <c r="B31" t="n">
-        <v>79199</v>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E31" t="n">
-        <v>228912</v>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Mörk kolflarnlav</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>Carbonicola myrmecina</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
-      <c r="P31" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q31" t="n">
-        <v>597961</v>
-      </c>
-      <c r="R31" t="n">
-        <v>7071725</v>
-      </c>
-      <c r="S31" t="n">
-        <v>10</v>
-      </c>
-      <c r="T31" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U31" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V31" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W31" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y31" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AA31" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
-      <c r="AD31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG31" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT31" t="inlineStr"/>
-      <c r="AW31" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>https://artportalen.se/Sighting/135277154</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>135277158</v>
-      </c>
-      <c r="B32" t="n">
-        <v>79464</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E32" t="n">
-        <v>260591</v>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Talltagel</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>Bryoria fremontii</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
-      <c r="P32" t="inlineStr">
-        <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
-        </is>
-      </c>
-      <c r="Q32" t="n">
-        <v>598024</v>
-      </c>
-      <c r="R32" t="n">
-        <v>7071673</v>
-      </c>
-      <c r="S32" t="n">
-        <v>10</v>
-      </c>
-      <c r="T32" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V32" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W32" t="inlineStr">
-        <is>
-          <t>Junsele</t>
-        </is>
-      </c>
-      <c r="Y32" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AA32" t="inlineStr">
-        <is>
-          <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
-      <c r="AD32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG32" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT32" t="inlineStr"/>
-      <c r="AW32" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>Anne-Katrin Würthele</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
-      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135277158</t>
         </is>
@@ -4196,18 +2756,6 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 27584-2026 artfynd.xlsx
+++ b/artfynd/A 27584-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ20"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -782,7 +782,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>135277159</v>
+        <v>135261483</v>
       </c>
       <c r="B3" t="n">
         <v>92050</v>
@@ -813,17 +813,17 @@
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>598084</v>
+        <v>597962</v>
       </c>
       <c r="R3" t="n">
-        <v>7071706</v>
+        <v>7071674</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -852,7 +852,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -862,7 +862,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>18:10</t>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -877,65 +877,65 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277159</t>
+          <t>https://artportalen.se/Sighting/135261483</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>135255201</v>
+        <v>135261485</v>
       </c>
       <c r="B4" t="n">
-        <v>92013</v>
+        <v>92050</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>597994</v>
+        <v>597961</v>
       </c>
       <c r="R4" t="n">
-        <v>7071669</v>
+        <v>7071670</v>
       </c>
       <c r="S4" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -962,9 +962,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>17:54</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>17:54</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -979,65 +989,65 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255201</t>
+          <t>https://artportalen.se/Sighting/135261485</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>135256316</v>
+        <v>135277159</v>
       </c>
       <c r="B5" t="n">
-        <v>79441</v>
+        <v>92050</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>598257</v>
+        <v>598084</v>
       </c>
       <c r="R5" t="n">
-        <v>7071764</v>
+        <v>7071706</v>
       </c>
       <c r="S5" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1064,9 +1074,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>18:10</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>18:10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1081,62 +1101,62 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256316</t>
+          <t>https://artportalen.se/Sighting/135277159</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>135256701</v>
+        <v>135255201</v>
       </c>
       <c r="B6" t="n">
-        <v>79441</v>
+        <v>92013</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>598315</v>
+        <v>597994</v>
       </c>
       <c r="R6" t="n">
-        <v>7071766</v>
+        <v>7071669</v>
       </c>
       <c r="S6" t="n">
         <v>15</v>
@@ -1194,13 +1214,13 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256701</t>
+          <t>https://artportalen.se/Sighting/135255201</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>135277153</v>
+        <v>135256316</v>
       </c>
       <c r="B7" t="n">
         <v>79441</v>
@@ -1231,17 +1251,17 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>597958</v>
+        <v>598257</v>
       </c>
       <c r="R7" t="n">
-        <v>7071702</v>
+        <v>7071764</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1268,19 +1288,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>17:45</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>17:45</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1295,65 +1305,65 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277153</t>
+          <t>https://artportalen.se/Sighting/135256316</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>135277160</v>
+        <v>135256701</v>
       </c>
       <c r="B8" t="n">
-        <v>83428</v>
+        <v>79441</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>598111</v>
+        <v>598315</v>
       </c>
       <c r="R8" t="n">
-        <v>7071757</v>
+        <v>7071766</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1380,19 +1390,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>18:25</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>18:25</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1407,65 +1407,68 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277160</t>
+          <t>https://artportalen.se/Sighting/135256701</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135255152</v>
+        <v>135261486</v>
       </c>
       <c r="B9" t="n">
-        <v>79198</v>
+        <v>79441</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>597979</v>
+        <v>598012</v>
       </c>
       <c r="R9" t="n">
-        <v>7071668</v>
+        <v>7071666</v>
       </c>
       <c r="S9" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1492,82 +1495,108 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>17:58</t>
+        </is>
+      </c>
       <c r="AD9" t="b">
         <v>0</v>
       </c>
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255152</t>
+          <t>https://artportalen.se/Sighting/135261486</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135256249</v>
+        <v>135277153</v>
       </c>
       <c r="B10" t="n">
-        <v>79198</v>
+        <v>79441</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>598246</v>
+        <v>597958</v>
       </c>
       <c r="R10" t="n">
-        <v>7071730</v>
+        <v>7071702</v>
       </c>
       <c r="S10" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1594,9 +1623,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>17:45</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1611,27 +1650,27 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256249</t>
+          <t>https://artportalen.se/Sighting/135277153</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135277156</v>
+        <v>135277160</v>
       </c>
       <c r="B11" t="n">
-        <v>80556</v>
+        <v>83428</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1639,21 +1678,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1663,10 +1702,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>598036</v>
+        <v>598111</v>
       </c>
       <c r="R11" t="n">
-        <v>7071669</v>
+        <v>7071757</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1698,7 +1737,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1708,7 +1747,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>17:57</t>
+          <t>18:25</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1734,54 +1773,54 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277156</t>
+          <t>https://artportalen.se/Sighting/135277160</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135277157</v>
+        <v>135255152</v>
       </c>
       <c r="B12" t="n">
-        <v>80561</v>
+        <v>79198</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>598034</v>
+        <v>597979</v>
       </c>
       <c r="R12" t="n">
-        <v>7071665</v>
+        <v>7071668</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1808,19 +1847,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>17:57</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>17:57</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1835,67 +1864,62 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277157</t>
+          <t>https://artportalen.se/Sighting/135255152</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135255036</v>
+        <v>135256249</v>
       </c>
       <c r="B13" t="n">
-        <v>57977</v>
+        <v>79198</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>597950</v>
+        <v>598246</v>
       </c>
       <c r="R13" t="n">
-        <v>7071688</v>
+        <v>7071730</v>
       </c>
       <c r="S13" t="n">
         <v>15</v>
@@ -1953,59 +1977,57 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255036</t>
+          <t>https://artportalen.se/Sighting/135256249</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135255232</v>
+        <v>135261492</v>
       </c>
       <c r="B14" t="n">
-        <v>57977</v>
+        <v>80556</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>597993</v>
+        <v>597943</v>
       </c>
       <c r="R14" t="n">
-        <v>7071670</v>
+        <v>7071647</v>
       </c>
       <c r="S14" t="n">
-        <v>15</v>
+        <v>3</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2032,87 +2054,108 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
       <c r="AE14" t="b">
         <v>0</v>
       </c>
+      <c r="AF14" t="inlineStr"/>
       <c r="AG14" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135255232</t>
+          <t>https://artportalen.se/Sighting/135261492</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135256280</v>
+        <v>135277156</v>
       </c>
       <c r="B15" t="n">
-        <v>57977</v>
+        <v>80556</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>598255</v>
+        <v>598036</v>
       </c>
       <c r="R15" t="n">
-        <v>7071787</v>
+        <v>7071669</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2139,9 +2182,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2156,27 +2209,27 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256280</t>
+          <t>https://artportalen.se/Sighting/135277156</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135277139</v>
+        <v>135261487</v>
       </c>
       <c r="B16" t="n">
-        <v>57977</v>
+        <v>80560</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2184,42 +2237,40 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6461</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Norrlandslav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Nephroma arcticum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Torss.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-kullberget, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>597949</v>
+        <v>598020</v>
       </c>
       <c r="R16" t="n">
-        <v>7071707</v>
+        <v>7071672</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2248,7 +2299,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2258,7 +2309,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>17:43</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2267,76 +2318,72 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
+      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Markus Borja, William Lord</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277139</t>
+          <t>https://artportalen.se/Sighting/135261487</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135256904</v>
+        <v>135277157</v>
       </c>
       <c r="B17" t="n">
-        <v>57980</v>
+        <v>80561</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>598036</v>
+        <v>598034</v>
       </c>
       <c r="R17" t="n">
-        <v>7071747</v>
+        <v>7071665</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2363,14 +2410,19 @@
           <t>2026-07-19</t>
         </is>
       </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>17:57</t>
+        </is>
+      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack, gran</t>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>17:57</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2385,71 +2437,67 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Daniel Rutschman</t>
+          <t>Anne-Katrin Würthele</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256904</t>
+          <t>https://artportalen.se/Sighting/135277157</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135256186</v>
+        <v>135255036</v>
       </c>
       <c r="B18" t="n">
-        <v>99276</v>
+        <v>57977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>blomning</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>598186</v>
+        <v>597950</v>
       </c>
       <c r="R18" t="n">
-        <v>7071740</v>
+        <v>7071688</v>
       </c>
       <c r="S18" t="n">
         <v>15</v>
@@ -2507,54 +2555,59 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135256186</t>
+          <t>https://artportalen.se/Sighting/135255036</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135277154</v>
+        <v>135255232</v>
       </c>
       <c r="B19" t="n">
-        <v>79199</v>
+        <v>57977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>597961</v>
+        <v>597993</v>
       </c>
       <c r="R19" t="n">
-        <v>7071725</v>
+        <v>7071670</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2581,19 +2634,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2608,65 +2651,70 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135277154</t>
+          <t>https://artportalen.se/Sighting/135255232</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135277158</v>
+        <v>135256280</v>
       </c>
       <c r="B20" t="n">
-        <v>79464</v>
+        <v>57977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>260591</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltagel</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Bryoria fremontii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå Kullberg 1:3, Ång</t>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>598024</v>
+        <v>598255</v>
       </c>
       <c r="R20" t="n">
-        <v>7071673</v>
+        <v>7071787</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2693,19 +2741,9 @@
           <t>2026-07-19</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>18:02</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2026-07-19</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>18:02</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2720,16 +2758,1418 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Anne-Katrin Würthele</t>
+          <t>Daniel Rutschman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256280</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>135261489</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>598336</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7071734</v>
+      </c>
+      <c r="S21" t="n">
+        <v>3</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261489</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>135277139</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57977</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>597949</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7071707</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:43</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277139</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>135256904</v>
+      </c>
+      <c r="B23" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Lill-Kullberget, Lill-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>598036</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7071747</v>
+      </c>
+      <c r="S23" t="n">
+        <v>15</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Färska ringhack, gran</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256904</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>135261482</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>597948</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7071677</v>
+      </c>
+      <c r="S24" t="n">
+        <v>3</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>17:49</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261482</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>135261491</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57980</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>597985</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7071632</v>
+      </c>
+      <c r="S25" t="n">
+        <v>3</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>19:11</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261491</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>135261493</v>
+      </c>
+      <c r="B26" t="n">
+        <v>58141</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>597900</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7071691</v>
+      </c>
+      <c r="S26" t="n">
+        <v>3</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Markus Borja, William Lord, Elin Pöllänen</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261493</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>135256186</v>
+      </c>
+      <c r="B27" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Stor-Kullberget, Stor-Kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>598186</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7071740</v>
+      </c>
+      <c r="S27" t="n">
+        <v>15</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Daniel Rutschman</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135256186</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>135261481</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7071680</v>
+      </c>
+      <c r="S28" t="n">
+        <v>3</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>17:45</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261481</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>135261488</v>
+      </c>
+      <c r="B29" t="n">
+        <v>98138</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>598051</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7071709</v>
+      </c>
+      <c r="S29" t="n">
+        <v>3</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:08</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261488</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>135261490</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Lill-kullberget, Ång</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>597995</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7071636</v>
+      </c>
+      <c r="S30" t="n">
+        <v>3</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>19:06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Markus Borja</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Markus Borja, Elin Pöllänen, William Lord</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135261490</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>135277154</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>597961</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7071725</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135277154</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>135277158</v>
+      </c>
+      <c r="B32" t="n">
+        <v>79464</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>260591</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Talltagel</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Bryoria fremontii</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Tuck.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Sollefteå Kullberg 1:3, Ång</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>598024</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7071673</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Junsele</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-07-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:02</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Anne-Katrin Würthele</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135277158</t>
         </is>
@@ -2756,6 +4196,18 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
